--- a/output/Data and Chart Outputs/germany_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/germany_power_capacity_monthly.xlsx
@@ -1031,7 +1031,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bundesnetzagentur Marktstammdatenregister (MaStR) Gesamtdatenexport, www.marktstammdatenregister.de/MaStR/Datendownload, Datenlizenz Deutschland - Namensnennung 2.0. Export read: Gesamtdatenexport_20261012_26.2.zip (last complete month Sep 2026; 9,600,475 units parsed in 228 s).</t>
+          <t>Bundesnetzagentur Marktstammdatenregister (MaStR) Gesamtdatenexport, www.marktstammdatenregister.de/MaStR/Datendownload, Datenlizenz Deutschland - Namensnennung 2.0. Export read: Gesamtdatenexport_20261012_26.2.zip (last complete month Sep 2026; 9,600,475 units parsed in 235 s).</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,7 +1577,7 @@
           <t>Gesamtdatenexport_20261012_26.2.zip</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
         <v>46307</v>
       </c>
       <c r="D3" t="n">
@@ -1586,7 +1586,31 @@
       <c r="E3" t="n">
         <v>228</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="5" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gesamtdatenexport_20261012_26.2.zip</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9600475</v>
+      </c>
+      <c r="E4" t="n">
+        <v>235</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>46266</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/germany_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/germany_power_capacity_monthly.xlsx
@@ -29,8 +29,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -70,14 +70,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1020,7 +1021,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1035,7 +1035,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1057,7 +1056,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -1072,7 +1070,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
@@ -1679,7 +1676,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="7" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1708,7 +1705,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="7" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1737,7 +1734,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="7" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1766,7 +1763,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="7" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1795,7 +1792,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="7" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1824,7 +1821,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="7" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1853,7 +1850,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="7" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1882,7 +1879,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1911,7 +1908,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1940,7 +1937,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1969,7 +1966,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1998,7 +1995,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2027,7 +2024,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2056,7 +2053,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2085,7 +2082,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2114,7 +2111,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2143,7 +2140,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="7" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2172,7 +2169,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="7" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2201,7 +2198,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="7" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2230,7 +2227,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="7" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2259,7 +2256,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="7" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2288,7 +2285,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="7" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2317,7 +2314,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="7" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2346,7 +2343,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="7" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2375,7 +2372,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="7" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2404,7 +2401,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="7" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2433,7 +2430,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="7" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2462,7 +2459,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="7" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2491,7 +2488,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="7" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2520,7 +2517,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="7" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2549,7 +2546,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="7" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2578,7 +2575,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="7" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2607,7 +2604,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="7" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2636,7 +2633,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="7" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2665,7 +2662,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="7" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2694,7 +2691,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="7" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2723,7 +2720,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="7" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2752,7 +2749,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="7" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2781,7 +2778,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="7" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2810,7 +2807,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="7" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2839,7 +2836,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="7" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2868,7 +2865,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="7" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2897,7 +2894,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="7" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2926,7 +2923,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="7" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2955,7 +2952,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="7" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2984,7 +2981,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="7" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -3013,7 +3010,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="7" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -3042,7 +3039,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="7" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -3071,7 +3068,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -3100,7 +3097,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -3129,7 +3126,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3158,7 +3155,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -3187,7 +3184,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -3216,7 +3213,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -3245,7 +3242,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3274,7 +3271,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3303,7 +3300,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -3332,7 +3329,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -3361,7 +3358,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3390,7 +3387,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3419,7 +3416,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -3448,7 +3445,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -3477,7 +3474,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -3506,7 +3503,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -3535,7 +3532,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3564,7 +3561,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3593,7 +3590,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="7" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -3622,7 +3619,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="7" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -3651,7 +3648,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="7" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -3715,7 +3712,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="7" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -3726,7 +3723,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="7" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -3737,7 +3734,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="7" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -3748,7 +3745,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="7" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -3759,7 +3756,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="7" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -3770,7 +3767,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="7" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -3781,7 +3778,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="7" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -3792,7 +3789,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -3803,7 +3800,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3814,7 +3811,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -3825,7 +3822,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -3836,7 +3833,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -3847,7 +3844,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -3858,7 +3855,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3869,7 +3866,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3880,7 +3877,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3891,7 +3888,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="7" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -3902,7 +3899,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="7" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -3913,7 +3910,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="7" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -3924,7 +3921,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="7" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -3935,7 +3932,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="7" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -3946,7 +3943,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="7" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3957,7 +3954,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="7" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3968,7 +3965,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="7" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3979,7 +3976,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="7" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3990,7 +3987,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="7" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -4001,7 +3998,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="7" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -4012,7 +4009,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="7" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -4023,7 +4020,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="7" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -4034,7 +4031,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="7" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -4045,7 +4042,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="7" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -4056,7 +4053,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="7" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -4067,7 +4064,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="7" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -4078,7 +4075,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="7" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -4089,7 +4086,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="7" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -4100,7 +4097,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="7" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -4111,7 +4108,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="7" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -4122,7 +4119,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="7" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -4133,7 +4130,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="7" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -4144,7 +4141,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="7" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -4155,7 +4152,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="7" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -4166,7 +4163,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="7" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -4177,7 +4174,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="7" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -4188,7 +4185,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="7" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -4199,7 +4196,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="7" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -4210,7 +4207,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="7" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -4221,7 +4218,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="7" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -4232,7 +4229,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="7" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -4243,7 +4240,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -4254,7 +4251,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -4265,7 +4262,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -4276,7 +4273,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -4287,7 +4284,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -4298,7 +4295,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -4309,7 +4306,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -4320,7 +4317,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -4331,7 +4328,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -4342,7 +4339,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -4353,7 +4350,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -4364,7 +4361,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -4375,7 +4372,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -4386,7 +4383,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -4397,7 +4394,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -4408,7 +4405,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -4419,7 +4416,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -4430,7 +4427,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -4441,7 +4438,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="7" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -4452,7 +4449,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="7" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -4463,7 +4460,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="7" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">

--- a/output/Data and Chart Outputs/germany_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/germany_power_capacity_monthly.xlsx
@@ -29,8 +29,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -70,15 +70,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1021,6 +1020,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1031,10 +1031,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bundesnetzagentur Marktstammdatenregister (MaStR) Gesamtdatenexport, www.marktstammdatenregister.de/MaStR/Datendownload, Datenlizenz Deutschland - Namensnennung 2.0. Export read: Gesamtdatenexport_20261012_26.2.zip (last complete month Sep 2026; 9,600,475 units parsed in 235 s).</t>
+          <t>Bundesnetzagentur Marktstammdatenregister (MaStR) Gesamtdatenexport, www.marktstammdatenregister.de/MaStR/Datendownload, Datenlizenz Deutschland - Namensnennung 2.0. Export read: Gesamtdatenexport_20261012_26.2.zip (last complete month Sep 2026; 9,600,475 units parsed in 236 s).</t>
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1056,6 +1057,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -1070,6 +1072,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
@@ -1509,7 +1512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,7 +1601,7 @@
           <t>Gesamtdatenexport_20261012_26.2.zip</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>46307</v>
       </c>
       <c r="D4" t="n">
@@ -1607,7 +1610,31 @@
       <c r="E4" t="n">
         <v>235</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="5" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gesamtdatenexport_20261012_26.2.zip</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9600475</v>
+      </c>
+      <c r="E5" t="n">
+        <v>236</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>46266</v>
       </c>
     </row>
@@ -1676,7 +1703,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="4" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1705,7 +1732,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="4" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1734,7 +1761,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="4" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1763,7 +1790,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="4" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1792,7 +1819,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="4" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1821,7 +1848,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="4" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1850,7 +1877,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="4" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1879,7 +1906,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="4" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1908,7 +1935,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="4" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1937,7 +1964,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="4" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1966,7 +1993,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="4" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1995,7 +2022,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="4" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2024,7 +2051,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="4" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2053,7 +2080,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="4" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2082,7 +2109,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="4" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2111,7 +2138,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="4" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2140,7 +2167,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="4" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2169,7 +2196,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="4" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2198,7 +2225,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="4" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2227,7 +2254,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="4" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2256,7 +2283,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="4" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2285,7 +2312,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="4" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2314,7 +2341,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="4" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2343,7 +2370,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="4" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2372,7 +2399,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="4" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2401,7 +2428,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="4" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2430,7 +2457,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="4" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2459,7 +2486,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="4" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2488,7 +2515,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="4" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2517,7 +2544,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="4" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2546,7 +2573,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="4" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2575,7 +2602,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="4" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2604,7 +2631,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="4" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2633,7 +2660,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="4" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2662,7 +2689,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="4" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2691,7 +2718,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="4" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2720,7 +2747,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="4" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2749,7 +2776,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="4" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2778,7 +2805,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="4" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2807,7 +2834,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="4" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2836,7 +2863,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="4" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2865,7 +2892,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="4" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2894,7 +2921,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="4" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2923,7 +2950,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="4" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2952,7 +2979,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="4" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2981,7 +3008,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="4" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -3010,7 +3037,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="4" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -3039,7 +3066,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="4" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -3068,7 +3095,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="4" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -3097,7 +3124,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="4" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -3126,7 +3153,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="4" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3155,7 +3182,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="4" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -3184,7 +3211,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="4" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -3213,7 +3240,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="4" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -3242,7 +3269,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="4" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3271,7 +3298,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="4" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3300,7 +3327,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="4" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -3329,7 +3356,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="4" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -3358,7 +3385,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="4" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3387,7 +3414,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="4" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3416,7 +3443,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="4" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -3445,7 +3472,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="4" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -3474,7 +3501,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n">
+      <c r="A64" s="4" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -3503,7 +3530,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="4" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -3532,7 +3559,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="n">
+      <c r="A66" s="4" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3561,7 +3588,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="4" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3590,7 +3617,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="4" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -3619,7 +3646,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="4" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -3648,7 +3675,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="4" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -3712,7 +3739,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="4" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -3723,7 +3750,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="4" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -3734,7 +3761,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="4" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -3745,7 +3772,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="4" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -3756,7 +3783,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="4" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -3767,7 +3794,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="4" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -3778,7 +3805,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="4" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -3789,7 +3816,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="4" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -3800,7 +3827,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="4" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3811,7 +3838,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="4" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -3822,7 +3849,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="4" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -3833,7 +3860,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="4" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -3844,7 +3871,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="4" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -3855,7 +3882,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="4" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3866,7 +3893,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="4" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3877,7 +3904,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="4" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3888,7 +3915,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="4" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -3899,7 +3926,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="4" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -3910,7 +3937,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="4" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -3921,7 +3948,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="4" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -3932,7 +3959,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="4" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -3943,7 +3970,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="4" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3954,7 +3981,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="4" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3965,7 +3992,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="4" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3976,7 +4003,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="4" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3987,7 +4014,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="4" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3998,7 +4025,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="4" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -4009,7 +4036,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="4" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -4020,7 +4047,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="4" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -4031,7 +4058,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="4" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -4042,7 +4069,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="4" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -4053,7 +4080,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="4" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -4064,7 +4091,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="4" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -4075,7 +4102,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="4" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -4086,7 +4113,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="4" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -4097,7 +4124,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="4" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -4108,7 +4135,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="4" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -4119,7 +4146,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="4" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -4130,7 +4157,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="4" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -4141,7 +4168,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="4" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -4152,7 +4179,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="4" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -4163,7 +4190,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="4" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -4174,7 +4201,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="4" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -4185,7 +4212,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="4" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -4196,7 +4223,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="4" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -4207,7 +4234,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="4" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -4218,7 +4245,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="4" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -4229,7 +4256,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="4" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -4240,7 +4267,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="4" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -4251,7 +4278,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="4" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -4262,7 +4289,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="4" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -4273,7 +4300,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="4" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -4284,7 +4311,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="4" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -4295,7 +4322,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="4" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -4306,7 +4333,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="4" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -4317,7 +4344,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="4" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -4328,7 +4355,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="4" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -4339,7 +4366,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="4" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -4350,7 +4377,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="4" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -4361,7 +4388,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="4" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -4372,7 +4399,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="4" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -4383,7 +4410,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="4" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -4394,7 +4421,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n">
+      <c r="A64" s="4" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -4405,7 +4432,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="4" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -4416,7 +4443,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="n">
+      <c r="A66" s="4" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -4427,7 +4454,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="4" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -4438,7 +4465,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="4" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -4449,7 +4476,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="4" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -4460,7 +4487,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="4" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -12499,7 +12526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12530,12 +12557,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Windenergie auf See</t>
+          <t>Windkraft auf See</t>
         </is>
       </c>
     </row>
@@ -12545,17 +12572,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wind onshore (WindAnLandOderAufSee)</t>
+          <t>Wind offshore (WindAnLandOderAufSee)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>889</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>General Electric Deutschland Holding GmbH</t>
+          <t>Windenergie auf See</t>
         </is>
       </c>
     </row>
@@ -12570,12 +12597,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NEG Micon Deutschland GmbH</t>
+          <t>Windenergie an Land</t>
         </is>
       </c>
     </row>
@@ -12585,17 +12612,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wind onshore (WindAnLandOderAufSee)</t>
+          <t>Pumped storage (hydro Art / storage Technologie)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pfleiderer Deutschland GmbH</t>
+          <t>Pumpspeicheranlage mit natürlichem Zufluss</t>
         </is>
       </c>
     </row>
@@ -12605,17 +12632,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wind onshore (WindAnLandOderAufSee)</t>
+          <t>Pumped storage (hydro Art / storage Technologie)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senvion Deutschland GmbH</t>
+          <t>Pumpspeicheranlage ohne natürlichen Zufluss</t>
         </is>
       </c>
     </row>
@@ -12625,17 +12652,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wind onshore (WindAnLandOderAufSee)</t>
+          <t>Pumped storage (hydro Art / storage Technologie)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SMG POLAND SP Z O O</t>
+          <t>Pumpspeicher</t>
         </is>
       </c>
     </row>
@@ -12645,17 +12672,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wind onshore (WindAnLandOderAufSee)</t>
+          <t>Pumped storage (hydro Art / storage Technologie)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vestas Deutschland GmbH</t>
+          <t>Pumpspeicheranlage ohne natürlichen Zufluss</t>
         </is>
       </c>
     </row>
@@ -12665,17 +12692,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wind onshore (WindAnLandOderAufSee)</t>
+          <t>Pumped storage (hydro Art / storage Technologie)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VWA-Deutschland GmbH Freude am Strom</t>
+          <t>Pumpspeicheranlage mit natürlichem Zufluss</t>
         </is>
       </c>
     </row>
@@ -12685,17 +12712,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wind onshore (WindAnLandOderAufSee)</t>
+          <t>Battery (storage Technologie)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>524</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Windenergie an Land</t>
+          <t>Batterie</t>
         </is>
       </c>
     </row>
@@ -12705,17 +12732,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pumped storage (hydro Art / storage Technologie)</t>
+          <t>Verbrennung Energietraeger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pumpspeicheranlage mit natürlichem Zufluss</t>
+          <t>Steinkohle -&gt; Coal (hard)</t>
         </is>
       </c>
     </row>
@@ -12725,17 +12752,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pumped storage (hydro Art / storage Technologie)</t>
+          <t>Verbrennung Energietraeger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pumpspeicheranlage ohne natürlichen Zufluss</t>
+          <t>Braunkohle -&gt; Lignite</t>
         </is>
       </c>
     </row>
@@ -12745,17 +12772,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pumped storage (hydro Art / storage Technologie)</t>
+          <t>Verbrennung Energietraeger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pumpspeicher</t>
+          <t>Mineralölprodukte -&gt; Oil</t>
         </is>
       </c>
     </row>
@@ -12765,17 +12792,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pumped storage (hydro Art / storage Technologie)</t>
+          <t>Verbrennung Energietraeger</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pumpspeicheranlage ohne natürlichen Zufluss</t>
+          <t>Erdgas -&gt; Gas (natural)</t>
         </is>
       </c>
     </row>
@@ -12785,17 +12812,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pumped storage (hydro Art / storage Technologie)</t>
+          <t>Verbrennung Energietraeger</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pumpspeicheranlage mit natürlichem Zufluss</t>
+          <t>andere Gase -&gt; Gas (other gases)</t>
         </is>
       </c>
     </row>
@@ -12805,17 +12832,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Battery (storage Technologie)</t>
+          <t>Verbrennung Energietraeger</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Batterie</t>
+          <t>nicht biogener Abfall -&gt; Other (non-biogenic waste)</t>
         </is>
       </c>
     </row>
@@ -12830,130 +12857,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2407</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Steinkohle -&gt; Coal (hard)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Verbrennung Energietraeger</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Braunkohle -&gt; Lignite</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Verbrennung Energietraeger</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mineralölprodukte -&gt; Oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Verbrennung Energietraeger</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2410</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Erdgas -&gt; Gas (natural)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Verbrennung Energietraeger</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>andere Gase -&gt; Gas (other gases)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Verbrennung Energietraeger</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>nicht biogener Abfall -&gt; Other (non-biogenic waste)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Verbrennung Energietraeger</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>2413</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Wärme -&gt; Other (heat)</t>
         </is>
